--- a/data/ground_truth/JPFA.xlsx
+++ b/data/ground_truth/JPFA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muhammadnajmirahmani/Belajar/ProjectDatasaur/data/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F867EF2A-A989-6E4C-AFF8-050426CA843E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{651BFBED-865C-A84B-BDC3-EE9A46191D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29300" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="72">
   <si>
     <t>Perusahaan</t>
   </si>
@@ -251,6 +251,9 @@
   </si>
   <si>
     <t>JPFA</t>
+  </si>
+  <si>
+    <t>11726575201.0</t>
   </si>
 </sst>
 </file>
@@ -274,11 +277,13 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -299,15 +304,15 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -338,7 +343,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -350,12 +355,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -373,9 +376,8 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
@@ -604,8 +606,7 @@
     <col min="9" max="9" width="19.5" customWidth="1"/>
     <col min="10" max="10" width="17.5" customWidth="1"/>
     <col min="11" max="11" width="17.1640625" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="8.6640625" customWidth="1"/>
+    <col min="12" max="15" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="32.83203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -619,7 +620,7 @@
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="13" t="s">
         <v>70</v>
       </c>
       <c r="E1" s="2"/>
@@ -760,383 +761,671 @@
       <c r="A4" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8">
+      <c r="B4" s="7">
+        <v>45145132000000</v>
+      </c>
+      <c r="C4" s="7">
+        <v>39333812000000</v>
+      </c>
+      <c r="D4" s="7">
+        <v>40060430000000</v>
+      </c>
+      <c r="E4" s="7">
+        <v>37302787000000</v>
+      </c>
+      <c r="F4" s="7">
+        <v>36374425000000</v>
+      </c>
+      <c r="G4" s="7">
+        <v>35552680000000</v>
+      </c>
+      <c r="H4" s="7">
+        <v>34666283000000</v>
+      </c>
+      <c r="I4" s="7">
+        <v>35534772000000</v>
+      </c>
+      <c r="J4" s="7">
+        <v>36108789000000</v>
+      </c>
+      <c r="K4" s="7">
+        <v>35759687000000</v>
+      </c>
+      <c r="L4" s="7">
+        <v>34109431000000</v>
+      </c>
+      <c r="M4" s="7">
+        <v>34846236000000</v>
+      </c>
+      <c r="N4" s="7">
+        <v>33884917000000</v>
+      </c>
+      <c r="O4" s="7">
+        <v>33273923000000</v>
+      </c>
+      <c r="P4" s="7">
         <v>32690887000000</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="Q4" s="14">
         <v>33230376000000</v>
       </c>
-      <c r="R4" s="5">
+      <c r="R4" s="7">
         <v>32815710000000</v>
       </c>
-      <c r="S4" s="5">
+      <c r="S4" s="7">
         <v>30134349000000</v>
       </c>
       <c r="T4" s="5"/>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9"/>
-      <c r="W4" s="9"/>
-      <c r="X4" s="9"/>
-      <c r="Y4" s="9"/>
-      <c r="Z4" s="9"/>
-      <c r="AA4" s="9"/>
+      <c r="U4" s="8"/>
+      <c r="V4" s="8"/>
+      <c r="W4" s="8"/>
+      <c r="X4" s="8"/>
+      <c r="Y4" s="8"/>
+      <c r="Z4" s="8"/>
+      <c r="AA4" s="8"/>
     </row>
     <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="6"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
+      <c r="B5" s="7">
+        <v>24480974000000</v>
+      </c>
+      <c r="C5" s="7">
+        <v>20010798000000</v>
+      </c>
+      <c r="D5" s="7">
+        <v>21376175000000</v>
+      </c>
+      <c r="E5" s="7">
+        <v>19647365000000</v>
+      </c>
+      <c r="F5" s="7">
+        <v>18615142000000</v>
+      </c>
+      <c r="G5" s="7">
+        <v>17931724000000</v>
+      </c>
+      <c r="H5" s="7">
+        <v>17169254000000</v>
+      </c>
+      <c r="I5" s="7">
+        <v>18433129000000</v>
+      </c>
+      <c r="J5" s="7">
+        <v>18969703000000</v>
+      </c>
+      <c r="K5" s="7">
+        <v>18612251000000</v>
+      </c>
+      <c r="L5" s="7">
+        <v>17218323000000</v>
+      </c>
+      <c r="M5" s="7">
+        <v>18242374000000</v>
+      </c>
+      <c r="N5" s="7">
+        <v>17620797000000</v>
+      </c>
+      <c r="O5" s="7">
+        <v>17386622000000</v>
+      </c>
       <c r="P5" s="6">
         <v>17001468000000</v>
       </c>
       <c r="Q5" s="5">
         <v>17984770000000</v>
       </c>
-      <c r="R5" s="5">
+      <c r="R5" s="7">
         <v>18119607000000</v>
       </c>
-      <c r="S5" s="5">
+      <c r="S5" s="7">
         <v>15719276000000</v>
       </c>
       <c r="T5" s="5"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
+      <c r="U5" s="8"/>
+      <c r="V5" s="8"/>
+      <c r="W5" s="8"/>
+      <c r="X5" s="8"/>
+      <c r="Y5" s="8"/>
+      <c r="Z5" s="8"/>
+      <c r="AA5" s="8"/>
     </row>
     <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8">
+      <c r="B6" s="7">
+        <v>2596987000000</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1849630000000</v>
+      </c>
+      <c r="D6" s="7">
+        <v>3550006000000</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1720300000000</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1734965000000</v>
+      </c>
+      <c r="G6" s="7">
+        <v>1741131000000</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1353714000000</v>
+      </c>
+      <c r="I6" s="7">
+        <v>1363031000000</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1451708000000</v>
+      </c>
+      <c r="K6" s="7">
+        <v>1608811000000</v>
+      </c>
+      <c r="L6" s="7">
+        <v>1502603000000</v>
+      </c>
+      <c r="M6" s="7">
+        <v>1444543000000</v>
+      </c>
+      <c r="N6" s="7">
+        <v>1553646000000</v>
+      </c>
+      <c r="O6" s="7">
+        <v>1384693000000</v>
+      </c>
+      <c r="P6" s="7">
         <v>1811082000000</v>
       </c>
       <c r="Q6" s="5">
         <v>1219154000000</v>
       </c>
-      <c r="R6" s="20">
+      <c r="R6" s="7">
         <v>1097616000000</v>
       </c>
-      <c r="S6" s="5">
+      <c r="S6" s="7">
         <v>1139520000000</v>
       </c>
       <c r="T6" s="5"/>
-      <c r="U6" s="9"/>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
-      <c r="Y6" s="9"/>
-      <c r="Z6" s="9"/>
-      <c r="AA6" s="9"/>
+      <c r="U6" s="8"/>
+      <c r="V6" s="8"/>
+      <c r="W6" s="8"/>
+      <c r="X6" s="8"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="8"/>
+      <c r="AA6" s="8"/>
     </row>
     <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8">
+      <c r="B7" s="7">
+        <v>23811080000000</v>
+      </c>
+      <c r="C7" s="7">
+        <v>17309391000000</v>
+      </c>
+      <c r="D7" s="7">
+        <v>20041473000000</v>
+      </c>
+      <c r="E7" s="7">
+        <v>19028953000000</v>
+      </c>
+      <c r="F7" s="7">
+        <v>19306169000000</v>
+      </c>
+      <c r="G7" s="7">
+        <v>18267373000000</v>
+      </c>
+      <c r="H7" s="7">
+        <v>18093761000000</v>
+      </c>
+      <c r="I7" s="7">
+        <v>19046155000000</v>
+      </c>
+      <c r="J7" s="7">
+        <v>20468858000000</v>
+      </c>
+      <c r="K7" s="7">
+        <v>20935810000000</v>
+      </c>
+      <c r="L7" s="7">
+        <v>19942219000000</v>
+      </c>
+      <c r="M7" s="7">
+        <v>20699945000000</v>
+      </c>
+      <c r="N7" s="7">
+        <v>20592766000000</v>
+      </c>
+      <c r="O7" s="7">
+        <v>19699899000000</v>
+      </c>
+      <c r="P7" s="7">
         <v>19036110000000</v>
       </c>
       <c r="Q7" s="5">
         <v>19496543000000</v>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="7">
         <v>19279165000000</v>
       </c>
-      <c r="S7" s="5">
+      <c r="S7" s="7">
         <v>16426569000000</v>
       </c>
       <c r="T7" s="5"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
+      <c r="U7" s="8"/>
+      <c r="V7" s="8"/>
+      <c r="W7" s="8"/>
+      <c r="X7" s="8"/>
+      <c r="Y7" s="8"/>
+      <c r="Z7" s="8"/>
+      <c r="AA7" s="8"/>
     </row>
     <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8">
+      <c r="B8" s="7">
+        <v>10250260000000</v>
+      </c>
+      <c r="C8" s="7">
+        <v>3482047000000</v>
+      </c>
+      <c r="D8" s="7">
+        <v>3874778000000</v>
+      </c>
+      <c r="E8" s="7">
+        <v>4336636000000</v>
+      </c>
+      <c r="F8" s="7">
+        <v>4823586000000</v>
+      </c>
+      <c r="G8" s="7">
+        <v>3306295000000</v>
+      </c>
+      <c r="H8" s="7">
+        <v>3212701000000</v>
+      </c>
+      <c r="I8" s="7">
+        <v>4989557000000</v>
+      </c>
+      <c r="J8" s="7">
+        <v>5736420000000</v>
+      </c>
+      <c r="K8" s="7">
+        <v>5473392000000</v>
+      </c>
+      <c r="L8" s="7">
+        <v>4908678000000</v>
+      </c>
+      <c r="M8" s="7">
+        <v>5086472000000</v>
+      </c>
+      <c r="N8" s="7">
+        <v>6704555000000</v>
+      </c>
+      <c r="O8" s="7">
+        <v>5894230000000</v>
+      </c>
+      <c r="P8" s="7">
         <v>4424209000000</v>
       </c>
       <c r="Q8" s="5">
         <v>4097902000000</v>
       </c>
-      <c r="R8" s="5">
+      <c r="R8" s="7">
         <v>2939943000000</v>
       </c>
-      <c r="S8" s="5">
+      <c r="S8" s="7">
         <v>1655739000000</v>
       </c>
       <c r="T8" s="5"/>
-      <c r="U8" s="9"/>
-      <c r="V8" s="9"/>
-      <c r="W8" s="9"/>
-      <c r="X8" s="9"/>
-      <c r="Y8" s="9"/>
-      <c r="Z8" s="9"/>
-      <c r="AA8" s="9"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8"/>
     </row>
     <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8">
+      <c r="B9" s="7">
+        <v>19822694000000</v>
+      </c>
+      <c r="C9" s="7">
+        <v>20540824000000</v>
+      </c>
+      <c r="D9" s="7">
+        <v>18663756000000</v>
+      </c>
+      <c r="E9" s="7">
+        <v>17007979000000</v>
+      </c>
+      <c r="F9" s="7">
+        <v>15895876000000</v>
+      </c>
+      <c r="G9" s="7">
+        <v>16116296000000</v>
+      </c>
+      <c r="H9" s="7">
+        <v>15476838000000</v>
+      </c>
+      <c r="I9" s="7">
+        <v>15438143000000</v>
+      </c>
+      <c r="J9" s="7">
+        <v>14627138000000</v>
+      </c>
+      <c r="K9" s="7">
+        <v>13871752000000</v>
+      </c>
+      <c r="L9" s="7">
+        <v>13226291000000</v>
+      </c>
+      <c r="M9" s="7">
+        <v>13168497000000</v>
+      </c>
+      <c r="N9" s="7">
+        <v>12341379000000</v>
+      </c>
+      <c r="O9" s="7">
+        <v>12644364000000</v>
+      </c>
+      <c r="P9" s="7">
         <v>12748045000000</v>
       </c>
       <c r="Q9" s="5">
         <v>12807894000000</v>
       </c>
-      <c r="R9" s="16">
+      <c r="R9" s="7">
         <v>12602880000000</v>
       </c>
-      <c r="S9" s="5">
+      <c r="S9" s="7">
         <v>12794690000000</v>
       </c>
       <c r="T9" s="5"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8"/>
     </row>
     <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="5"/>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8">
+      <c r="B10" s="7">
+        <v>2475417000000</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1816410000000</v>
+      </c>
+      <c r="D10" s="7">
+        <v>4003999000000</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2411411000000</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1236264000000</v>
+      </c>
+      <c r="G10" s="7">
+        <v>680417000000</v>
+      </c>
+      <c r="H10" s="7">
+        <v>3018892000000</v>
+      </c>
+      <c r="I10" s="7">
+        <v>2095915000000</v>
+      </c>
+      <c r="J10" s="7">
+        <v>1479292000000</v>
+      </c>
+      <c r="K10" s="7">
+        <v>664823000000</v>
+      </c>
+      <c r="L10" s="7">
+        <v>929716000000</v>
+      </c>
+      <c r="M10" s="7">
+        <v>937259000000</v>
+      </c>
+      <c r="N10" s="7">
+        <v>81976000000</v>
+      </c>
+      <c r="O10" s="7">
+        <v>-249927000000</v>
+      </c>
+      <c r="P10" s="7">
         <v>1419855000000</v>
       </c>
       <c r="Q10" s="5">
         <v>1428249000000</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="7">
         <v>1111746000000</v>
       </c>
-      <c r="S10" s="5">
+      <c r="S10" s="7">
         <v>603739000000</v>
       </c>
       <c r="T10" s="5"/>
-      <c r="U10" s="9"/>
-      <c r="V10" s="9"/>
-      <c r="W10" s="9"/>
-      <c r="X10" s="9"/>
-      <c r="Y10" s="9"/>
-      <c r="Z10" s="9"/>
-      <c r="AA10" s="9"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
     </row>
     <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="5"/>
-      <c r="L11" s="5"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="5"/>
-      <c r="O11" s="5"/>
+      <c r="B11" s="7">
+        <v>35355127000000</v>
+      </c>
+      <c r="C11" s="7">
+        <v>17714001000000</v>
+      </c>
+      <c r="D11" s="7">
+        <v>60715806000000</v>
+      </c>
+      <c r="E11" s="7">
+        <v>43104381000000</v>
+      </c>
+      <c r="F11" s="7">
+        <v>27481591000000</v>
+      </c>
+      <c r="G11" s="7">
+        <v>14332271000000</v>
+      </c>
+      <c r="H11" s="7">
+        <v>55800849000000</v>
+      </c>
+      <c r="I11" s="7">
+        <v>41279935000000</v>
+      </c>
+      <c r="J11" s="7">
+        <v>27648515000000</v>
+      </c>
+      <c r="K11" s="7">
+        <v>13925495000000</v>
+      </c>
+      <c r="L11" s="7">
+        <v>51175898000000</v>
+      </c>
+      <c r="M11" s="7">
+        <v>37767422000000</v>
+      </c>
+      <c r="N11" s="7">
+        <v>24155760000000</v>
+      </c>
+      <c r="O11" s="7">
+        <v>11761795000000</v>
+      </c>
       <c r="P11" s="5">
         <v>48972085000000</v>
       </c>
       <c r="Q11" s="5">
         <v>36793282000000</v>
       </c>
-      <c r="R11" s="5">
+      <c r="R11" s="7">
         <v>24483172000000</v>
       </c>
-      <c r="S11" s="5">
+      <c r="S11" s="7">
         <v>12154001000000</v>
       </c>
       <c r="T11" s="5"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
+      <c r="U11" s="8"/>
+      <c r="V11" s="8"/>
+      <c r="W11" s="8"/>
+      <c r="X11" s="8"/>
+      <c r="Y11" s="8"/>
+      <c r="Z11" s="8"/>
+      <c r="AA11" s="8"/>
     </row>
     <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8">
+      <c r="B12" s="7">
+        <v>-2228148000000</v>
+      </c>
+      <c r="C12" s="7">
+        <v>2222864000000</v>
+      </c>
+      <c r="D12" s="7">
+        <v>5012140000000</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2205643000000</v>
+      </c>
+      <c r="F12" s="7">
+        <v>983795000000</v>
+      </c>
+      <c r="G12" s="7">
+        <v>894941000000</v>
+      </c>
+      <c r="H12" s="7">
+        <v>4860422000000</v>
+      </c>
+      <c r="I12" s="7">
+        <v>1686138000000</v>
+      </c>
+      <c r="J12" s="7">
+        <v>346831000000</v>
+      </c>
+      <c r="K12" s="7">
+        <v>182116000000</v>
+      </c>
+      <c r="L12" s="7">
+        <v>2371932000000</v>
+      </c>
+      <c r="M12" s="7">
+        <v>1301938000000</v>
+      </c>
+      <c r="N12" s="7">
+        <v>-511881000000</v>
+      </c>
+      <c r="O12" s="7">
+        <v>-1311329000000</v>
+      </c>
+      <c r="P12" s="7">
         <v>1426749000000</v>
       </c>
       <c r="Q12" s="5">
         <v>372047000000</v>
       </c>
-      <c r="R12" s="5">
+      <c r="R12" s="7">
         <v>436518000000</v>
       </c>
-      <c r="S12" s="22">
+      <c r="S12" s="7">
         <v>904913000000</v>
       </c>
       <c r="T12" s="5"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
+      <c r="U12" s="8"/>
+      <c r="V12" s="8"/>
+      <c r="W12" s="8"/>
+      <c r="X12" s="8"/>
+      <c r="Y12" s="8"/>
+      <c r="Z12" s="8"/>
+      <c r="AA12" s="8"/>
     </row>
     <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="5"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="Q13" s="5"/>
-      <c r="R13" s="5"/>
-      <c r="S13" s="5"/>
+      <c r="B13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="C13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="D13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="E13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="F13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="G13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="H13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="I13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="J13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="K13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="L13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="M13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="N13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="O13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="P13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="R13" s="7">
+        <v>11726575201</v>
+      </c>
+      <c r="S13" s="7">
+        <v>11726575201</v>
+      </c>
       <c r="T13" s="5"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
+      <c r="U13" s="8"/>
+      <c r="V13" s="8"/>
+      <c r="W13" s="8"/>
+      <c r="X13" s="8"/>
+      <c r="Y13" s="8"/>
+      <c r="Z13" s="8"/>
+      <c r="AA13" s="8"/>
     </row>
     <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
@@ -1181,103 +1470,103 @@
       <c r="T14" s="5">
         <v>725</v>
       </c>
-      <c r="U14" s="9">
+      <c r="U14" s="8">
         <v>570</v>
       </c>
-      <c r="V14" s="9">
+      <c r="V14" s="8">
         <v>570</v>
       </c>
       <c r="W14" s="4">
         <v>570</v>
       </c>
-      <c r="X14" s="9">
+      <c r="X14" s="8">
         <v>570</v>
       </c>
-      <c r="Y14" s="9">
+      <c r="Y14" s="8">
         <v>570</v>
       </c>
-      <c r="Z14" s="9">
+      <c r="Z14" s="8">
         <v>1140</v>
       </c>
-      <c r="AA14" s="9">
+      <c r="AA14" s="8">
         <v>1140</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="6" t="e">
+      <c r="B15" s="6">
         <f t="shared" ref="B15:AA15" si="0">B9/B13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C15" s="6" t="e">
+        <v>1690.407784048457</v>
+      </c>
+      <c r="C15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D15" s="6" t="e">
+        <v>1751.647317986615</v>
+      </c>
+      <c r="D15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E15" s="6" t="e">
+        <v>1591.577735194878</v>
+      </c>
+      <c r="E15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F15" s="6" t="e">
+        <v>1450.3790500187661</v>
+      </c>
+      <c r="F15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="6" t="e">
+        <v>1355.5429208900189</v>
+      </c>
+      <c r="G15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H15" s="6" t="e">
+        <v>1374.3395427699693</v>
+      </c>
+      <c r="H15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I15" s="6" t="e">
+        <v>1319.8088729845174</v>
+      </c>
+      <c r="I15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J15" s="6" t="e">
+        <v>1316.5091030741432</v>
+      </c>
+      <c r="J15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K15" s="6" t="e">
+        <v>1247.3495244163573</v>
+      </c>
+      <c r="K15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L15" s="6" t="e">
+        <v>1182.9329332930101</v>
+      </c>
+      <c r="L15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M15" s="6" t="e">
+        <v>1127.890349338493</v>
+      </c>
+      <c r="M15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N15" s="6" t="e">
+        <v>1122.9618856558425</v>
+      </c>
+      <c r="N15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O15" s="6" t="e">
+        <v>1052.4282485262681</v>
+      </c>
+      <c r="O15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P15" s="6" t="e">
+        <v>1078.2657155451263</v>
+      </c>
+      <c r="P15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q15" s="6" t="e">
+        <v>1087.1072569349058</v>
+      </c>
+      <c r="Q15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R15" s="6" t="e">
+        <v>1092.2109635989705</v>
+      </c>
+      <c r="R15" s="6">
         <f t="shared" si="0"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S15" s="6" t="e">
+        <v>1074.728109783091</v>
+      </c>
+      <c r="S15" s="6">
         <f>S9/S13</f>
-        <v>#DIV/0!</v>
+        <v>1091.0849741456409</v>
       </c>
       <c r="T15" s="6" t="e">
         <f t="shared" si="0"/>
@@ -1295,82 +1584,82 @@
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X15" s="12" t="e">
+      <c r="X15" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y15" s="12" t="e">
+      <c r="Y15" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z15" s="12" t="e">
+      <c r="Z15" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA15" s="12" t="e">
+      <c r="AA15" s="10" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="9" t="s">
         <v>59</v>
       </c>
       <c r="B16" s="6">
         <f t="shared" ref="B16:AA16" si="1">B5-B7</f>
-        <v>0</v>
+        <v>669894000000</v>
       </c>
       <c r="C16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2701407000000</v>
       </c>
       <c r="D16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1334702000000</v>
       </c>
       <c r="E16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>618412000000</v>
       </c>
       <c r="F16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-691027000000</v>
       </c>
       <c r="G16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-335649000000</v>
       </c>
       <c r="H16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-924507000000</v>
       </c>
       <c r="I16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-613026000000</v>
       </c>
       <c r="J16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-1499155000000</v>
       </c>
       <c r="K16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2323559000000</v>
       </c>
       <c r="L16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2723896000000</v>
       </c>
       <c r="M16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2457571000000</v>
       </c>
       <c r="N16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2971969000000</v>
       </c>
       <c r="O16" s="6">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-2313277000000</v>
       </c>
       <c r="P16" s="6">
         <f t="shared" si="1"/>
@@ -1404,534 +1693,534 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="X16" s="12">
+      <c r="X16" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y16" s="12">
+      <c r="Y16" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="12">
+      <c r="Z16" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="12">
+      <c r="AA16" s="10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="13" t="e">
+      <c r="B17" s="11">
         <f t="shared" ref="B17:AA17" si="2">B10/B4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C17" s="13" t="e">
+        <v>5.4832423571161561E-2</v>
+      </c>
+      <c r="C17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D17" s="13" t="e">
+        <v>4.6179353274988962E-2</v>
+      </c>
+      <c r="D17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E17" s="13" t="e">
+        <v>9.9948977082872051E-2</v>
+      </c>
+      <c r="E17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F17" s="13" t="e">
+        <v>6.4644258349919007E-2</v>
+      </c>
+      <c r="F17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G17" s="13" t="e">
+        <v>3.3987176429593043E-2</v>
+      </c>
+      <c r="G17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H17" s="13" t="e">
+        <v>1.9138275933066086E-2</v>
+      </c>
+      <c r="H17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I17" s="13" t="e">
+        <v>8.7084386866627728E-2</v>
+      </c>
+      <c r="I17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J17" s="13" t="e">
+        <v>5.8982086616455563E-2</v>
+      </c>
+      <c r="J17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K17" s="13" t="e">
+        <v>4.0967643639336672E-2</v>
+      </c>
+      <c r="K17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L17" s="13" t="e">
+        <v>1.8591409930405711E-2</v>
+      </c>
+      <c r="L17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M17" s="13" t="e">
+        <v>2.7256860426666162E-2</v>
+      </c>
+      <c r="M17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N17" s="13" t="e">
+        <v>2.6896993982362973E-2</v>
+      </c>
+      <c r="N17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O17" s="13" t="e">
+        <v>2.4192474781626291E-3</v>
+      </c>
+      <c r="O17" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P17" s="13">
+        <v>-7.5111972820277309E-3</v>
+      </c>
+      <c r="P17" s="11">
         <f t="shared" si="2"/>
         <v>4.3432746257389715E-2</v>
       </c>
-      <c r="Q17" s="13">
+      <c r="Q17" s="11">
         <f t="shared" si="2"/>
         <v>4.298022387709366E-2</v>
       </c>
-      <c r="R17" s="13">
+      <c r="R17" s="11">
         <f t="shared" si="2"/>
         <v>3.3878468574959984E-2</v>
       </c>
-      <c r="S17" s="13">
+      <c r="S17" s="11">
         <f t="shared" si="2"/>
         <v>2.0034910991440367E-2</v>
       </c>
-      <c r="T17" s="13" t="e">
+      <c r="T17" s="11" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U17" s="13" t="e">
+      <c r="U17" s="11" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V17" s="13" t="e">
+      <c r="V17" s="11" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W17" s="13" t="e">
+      <c r="W17" s="11" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X17" s="13" t="e">
+      <c r="X17" s="11" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y17" s="13" t="e">
+      <c r="Y17" s="11" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z17" s="13" t="e">
+      <c r="Z17" s="11" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA17" s="13" t="e">
+      <c r="AA17" s="11" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B18" s="13" t="e">
+      <c r="B18" s="11">
         <f t="shared" ref="B18:AA18" si="3">B10/B9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C18" s="13" t="e">
+        <v>0.12487793031562713</v>
+      </c>
+      <c r="C18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D18" s="13" t="e">
+        <v>8.8429266518227315E-2</v>
+      </c>
+      <c r="D18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E18" s="13" t="e">
+        <v>0.21453339831489437</v>
+      </c>
+      <c r="E18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F18" s="13" t="e">
+        <v>0.14178116047767933</v>
+      </c>
+      <c r="F18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G18" s="13" t="e">
+        <v>7.7772624799035919E-2</v>
+      </c>
+      <c r="G18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H18" s="13" t="e">
+        <v>4.2219192300761911E-2</v>
+      </c>
+      <c r="H18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I18" s="13" t="e">
+        <v>0.1950587064360304</v>
+      </c>
+      <c r="I18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J18" s="13" t="e">
+        <v>0.13576211853977516</v>
+      </c>
+      <c r="J18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K18" s="13" t="e">
+        <v>0.10113338644921516</v>
+      </c>
+      <c r="K18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L18" s="13" t="e">
+        <v>4.7926390264185804E-2</v>
+      </c>
+      <c r="L18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M18" s="13" t="e">
+        <v>7.0293024703599827E-2</v>
+      </c>
+      <c r="M18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N18" s="13" t="e">
+        <v>7.1174333714773982E-2</v>
+      </c>
+      <c r="N18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O18" s="13" t="e">
+        <v>6.6423695439545285E-3</v>
+      </c>
+      <c r="O18" s="11">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P18" s="13">
+        <v>-1.9765881463077145E-2</v>
+      </c>
+      <c r="P18" s="11">
         <f t="shared" si="3"/>
         <v>0.1113782544696069</v>
       </c>
-      <c r="Q18" s="13">
+      <c r="Q18" s="11">
         <f t="shared" si="3"/>
         <v>0.11151318085549428</v>
       </c>
-      <c r="R18" s="13">
+      <c r="R18" s="11">
         <f t="shared" si="3"/>
         <v>8.8213646404631321E-2</v>
       </c>
-      <c r="S18" s="13">
+      <c r="S18" s="11">
         <f t="shared" si="3"/>
         <v>4.7186684476138149E-2</v>
       </c>
-      <c r="T18" s="13" t="e">
+      <c r="T18" s="11" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U18" s="13" t="e">
+      <c r="U18" s="11" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V18" s="13" t="e">
+      <c r="V18" s="11" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W18" s="13" t="e">
+      <c r="W18" s="11" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X18" s="13" t="e">
+      <c r="X18" s="11" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y18" s="13" t="e">
+      <c r="Y18" s="11" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z18" s="13" t="e">
+      <c r="Z18" s="11" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA18" s="13" t="e">
+      <c r="AA18" s="11" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="14" t="e">
+      <c r="B19" s="12">
         <f t="shared" ref="B19:AA19" si="4">B14/B15</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C19" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="C19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D19" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="D19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E19" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F19" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="F19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G19" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H19" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="H19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I19" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="I19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J19" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="J19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K19" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="K19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L19" s="14" t="e">
+        <v>0.37533826940129839</v>
+      </c>
+      <c r="L19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M19" s="14" t="e">
+        <v>0.39720173176652473</v>
+      </c>
+      <c r="M19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N19" s="14" t="e">
+        <v>0.40428798679560773</v>
+      </c>
+      <c r="N19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O19" s="14" t="e">
+        <v>0.43518406185062464</v>
+      </c>
+      <c r="O19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P19" s="14" t="e">
+        <v>0.42104649480622358</v>
+      </c>
+      <c r="P19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q19" s="14" t="e">
+        <v>0.43050029977678927</v>
+      </c>
+      <c r="Q19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R19" s="14" t="e">
+        <v>0.53103294082383878</v>
+      </c>
+      <c r="R19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S19" s="14" t="e">
+        <v>0.56758541481074165</v>
+      </c>
+      <c r="S19" s="12">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T19" s="14" t="e">
+        <v>0.32261465269983097</v>
+      </c>
+      <c r="T19" s="12" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U19" s="14" t="e">
+      <c r="U19" s="12" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V19" s="14" t="e">
+      <c r="V19" s="12" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W19" s="14" t="e">
+      <c r="W19" s="12" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X19" s="12" t="e">
+      <c r="X19" s="10" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y19" s="12" t="e">
+      <c r="Y19" s="10" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z19" s="12" t="e">
+      <c r="Z19" s="10" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA19" s="12" t="e">
+      <c r="AA19" s="10" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="B20" s="14" t="e">
+      <c r="B20" s="12">
         <f t="shared" ref="B20:AA20" si="5">B14/B21</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C20" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="C20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D20" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="D20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E20" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="E20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F20" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G20" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H20" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="H20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I20" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="I20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J20" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="J20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K20" s="14" t="e">
+        <v>0</v>
+      </c>
+      <c r="K20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L20" s="14" t="e">
+        <v>7.831557255455964</v>
+      </c>
+      <c r="L20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M20" s="14" t="e">
+        <v>5.6506564263151331</v>
+      </c>
+      <c r="M20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N20" s="14" t="e">
+        <v>5.6802496868571017</v>
+      </c>
+      <c r="N20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O20" s="14" t="e">
+        <v>65.516388236288677</v>
+      </c>
+      <c r="O20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P20" s="14" t="e">
+        <v>-21.301680655767484</v>
+      </c>
+      <c r="P20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q20" s="14" t="e">
+        <v>3.8652096122970301</v>
+      </c>
+      <c r="Q20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R20" s="14" t="e">
+        <v>4.7620643295251739</v>
+      </c>
+      <c r="R20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S20" s="14" t="e">
+        <v>6.4342132758831605</v>
+      </c>
+      <c r="S20" s="12">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T20" s="14" t="e">
+        <v>6.836984973228498</v>
+      </c>
+      <c r="T20" s="12" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U20" s="14" t="e">
+      <c r="U20" s="12" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V20" s="14" t="e">
+      <c r="V20" s="12" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W20" s="14" t="e">
+      <c r="W20" s="12" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X20" s="12" t="e">
+      <c r="X20" s="10" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y20" s="12" t="e">
+      <c r="Y20" s="10" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z20" s="12" t="e">
+      <c r="Z20" s="10" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA20" s="12" t="e">
+      <c r="AA20" s="10" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="21" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B21" s="6" t="e">
+      <c r="B21" s="6">
         <f t="shared" ref="B21:AA21" si="6">B10/B13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C21" s="6" t="e">
+        <v>211.0946254613969</v>
+      </c>
+      <c r="C21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D21" s="6" t="e">
+        <v>154.89688752817645</v>
+      </c>
+      <c r="D21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E21" s="6" t="e">
+        <v>341.44658021368025</v>
+      </c>
+      <c r="E21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F21" s="6" t="e">
+        <v>205.63642484417477</v>
+      </c>
+      <c r="F21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G21" s="6" t="e">
+        <v>105.42413098536868</v>
+      </c>
+      <c r="G21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H21" s="6" t="e">
+        <v>58.023505442746533</v>
+      </c>
+      <c r="H21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I21" s="6" t="e">
+        <v>257.44021150715514</v>
+      </c>
+      <c r="I21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J21" s="6" t="e">
+        <v>178.7320649102449</v>
+      </c>
+      <c r="J21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K21" s="6" t="e">
+        <v>126.1486814900442</v>
+      </c>
+      <c r="K21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L21" s="6" t="e">
+        <v>56.693705417358878</v>
+      </c>
+      <c r="L21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M21" s="6" t="e">
+        <v>79.282824189002525</v>
+      </c>
+      <c r="M21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N21" s="6" t="e">
+        <v>79.926063998640785</v>
+      </c>
+      <c r="N21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O21" s="6" t="e">
+        <v>6.9906173452082907</v>
+      </c>
+      <c r="O21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P21" s="6" t="e">
+        <v>-21.312872319165031</v>
+      </c>
+      <c r="P21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q21" s="6" t="e">
+        <v>121.08010869865227</v>
+      </c>
+      <c r="Q21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R21" s="6" t="e">
+        <v>121.79591871616566</v>
+      </c>
+      <c r="R21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="S21" s="6" t="e">
+        <v>94.805685457523381</v>
+      </c>
+      <c r="S21" s="6">
         <f t="shared" si="6"/>
-        <v>#DIV/0!</v>
+        <v>51.484682411665709</v>
       </c>
       <c r="T21" s="6" t="e">
         <f t="shared" si="6"/>
@@ -1949,134 +2238,165 @@
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X21" s="12" t="e">
+      <c r="X21" s="10" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y21" s="12" t="e">
+      <c r="Y21" s="10" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z21" s="12" t="e">
+      <c r="Z21" s="10" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA21" s="12" t="e">
+      <c r="AA21" s="10" t="e">
         <f t="shared" si="6"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="B22" s="13" t="e">
+      <c r="B22" s="11">
         <f t="shared" ref="B22:AA22" si="7">B7/B9</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="C22" s="13" t="e">
+        <v>1.2012030251791204</v>
+      </c>
+      <c r="C22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="D22" s="13" t="e">
+        <v>0.84268240650910597</v>
+      </c>
+      <c r="D22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E22" s="13" t="e">
+        <v>1.0738177781578371</v>
+      </c>
+      <c r="E22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F22" s="13" t="e">
+        <v>1.1188250526414691</v>
+      </c>
+      <c r="F22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G22" s="13" t="e">
+        <v>1.2145394818127671</v>
+      </c>
+      <c r="G22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H22" s="13" t="e">
+        <v>1.1334721700321215</v>
+      </c>
+      <c r="H22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I22" s="13" t="e">
+        <v>1.1690864115783857</v>
+      </c>
+      <c r="I22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J22" s="13" t="e">
+        <v>1.2337076421691391</v>
+      </c>
+      <c r="J22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K22" s="13" t="e">
+        <v>1.3993754622401184</v>
+      </c>
+      <c r="K22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="L22" s="13" t="e">
+        <v>1.5092405054530964</v>
+      </c>
+      <c r="L22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="M22" s="13" t="e">
+        <v>1.5077710750504432</v>
+      </c>
+      <c r="M22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N22" s="13" t="e">
+        <v>1.5719292034618682</v>
+      </c>
+      <c r="N22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O22" s="13" t="e">
+        <v>1.6685952193835065</v>
+      </c>
+      <c r="O22" s="11">
         <f t="shared" si="7"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P22" s="13">
+        <v>1.5579984094099157</v>
+      </c>
+      <c r="P22" s="11">
         <f t="shared" si="7"/>
         <v>1.4932572013983321</v>
       </c>
-      <c r="Q22" s="13">
+      <c r="Q22" s="11">
         <f t="shared" si="7"/>
         <v>1.5222286349340493</v>
       </c>
-      <c r="R22" s="13">
+      <c r="R22" s="11">
         <f t="shared" si="7"/>
         <v>1.5297428048192159</v>
       </c>
-      <c r="S22" s="13">
+      <c r="S22" s="11">
         <f t="shared" si="7"/>
         <v>1.283858303718183</v>
       </c>
-      <c r="T22" s="13" t="e">
+      <c r="T22" s="11" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U22" s="13" t="e">
+      <c r="U22" s="11" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="V22" s="13" t="e">
+      <c r="V22" s="11" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W22" s="13" t="e">
+      <c r="W22" s="11" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="X22" s="13" t="e">
+      <c r="X22" s="11" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Y22" s="13" t="e">
+      <c r="Y22" s="11" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z22" s="13" t="e">
+      <c r="Z22" s="11" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="AA22" s="13" t="e">
+      <c r="AA22" s="11" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K24" s="19">
+        <v>45145132000000</v>
+      </c>
+      <c r="L24" s="19">
+        <v>24480974000000</v>
+      </c>
+      <c r="M24" s="19">
+        <v>2596987000000</v>
+      </c>
+      <c r="N24" s="19">
+        <v>23811080000000</v>
+      </c>
+      <c r="O24" s="19">
+        <v>10250260000000</v>
+      </c>
+      <c r="P24" s="19">
+        <v>19822694000000</v>
+      </c>
+      <c r="Q24" s="19">
+        <v>2475417000000</v>
+      </c>
+      <c r="R24" s="19">
+        <v>35355127000000</v>
+      </c>
+      <c r="S24" s="19">
+        <v>-2228148000000</v>
+      </c>
+      <c r="T24" s="19" t="s">
+        <v>71</v>
+      </c>
+    </row>
     <row r="25" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="26" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="27" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3084,27 +3404,27 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="18">
+      <c r="A2" s="16">
         <v>6.7299999999999999E-2</v>
       </c>
       <c r="B2">
         <f>1000/A2</f>
         <v>14858.841010401189</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="17">
         <v>247029168</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="14">
         <f>B2*C2</f>
         <v>3670567132243.6851</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="18">
         <v>3868963000000</v>
       </c>
-      <c r="G2" s="21">
+      <c r="G2" s="18">
         <v>555246000000</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="15">
         <f>F2+G2</f>
         <v>4424209000000</v>
       </c>

--- a/data/ground_truth/JPFA.xlsx
+++ b/data/ground_truth/JPFA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/muhammadnajmirahmani/Belajar/ProjectDatasaur/data/ground_truth/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1324681-C123-4F44-85F7-6682E19107A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E48B57F-8841-3745-8931-25897CB23A71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29300" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1363,37 +1363,37 @@
         <v>11704870701</v>
       </c>
       <c r="C13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="D13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="E13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="F13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="G13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="H13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="I13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="J13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="K13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="L13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="M13" s="20">
-        <v>11620308701</v>
+        <v>11627669901</v>
       </c>
       <c r="N13" s="20">
         <v>11620308701</v>
@@ -1515,47 +1515,47 @@
       </c>
       <c r="C15" s="6">
         <f t="shared" si="0"/>
-        <v>1767.6659483437247</v>
+        <v>1766.5468812658203</v>
       </c>
       <c r="D15" s="6">
         <f t="shared" si="0"/>
-        <v>1606.1325460651374</v>
+        <v>1605.1157419247759</v>
       </c>
       <c r="E15" s="6">
         <f t="shared" si="0"/>
-        <v>1463.6426137746546</v>
+        <v>1462.7160166059825</v>
       </c>
       <c r="F15" s="6">
         <f t="shared" si="0"/>
-        <v>1367.9392182267982</v>
+        <v>1367.0732085912523</v>
       </c>
       <c r="G15" s="6">
         <f t="shared" si="0"/>
-        <v>1386.9077332354425</v>
+        <v>1386.0297150862505</v>
       </c>
       <c r="H15" s="6">
         <f t="shared" si="0"/>
-        <v>1331.8783862143114</v>
+        <v>1331.0352058299286</v>
       </c>
       <c r="I15" s="6">
         <f t="shared" si="0"/>
-        <v>1328.5484402554168</v>
+        <v>1327.70736798026</v>
       </c>
       <c r="J15" s="6">
         <f t="shared" si="0"/>
-        <v>1258.7564045300487</v>
+        <v>1257.9595159252019</v>
       </c>
       <c r="K15" s="6">
         <f t="shared" si="0"/>
-        <v>1193.7507304609085</v>
+        <v>1192.9949953951655</v>
       </c>
       <c r="L15" s="6">
         <f t="shared" si="0"/>
-        <v>1138.2047878695164</v>
+        <v>1137.4842176128957</v>
       </c>
       <c r="M15" s="6">
         <f t="shared" si="0"/>
-        <v>1133.2312539052227</v>
+        <v>1132.5138322741245</v>
       </c>
       <c r="N15" s="6">
         <f t="shared" si="0"/>
@@ -1951,47 +1951,47 @@
       </c>
       <c r="C19" s="12">
         <f t="shared" si="4"/>
-        <v>1.0890066654300237</v>
+        <v>1.0896965262652074</v>
       </c>
       <c r="D19" s="12">
         <f t="shared" si="4"/>
-        <v>1.5752124606392197</v>
+        <v>1.5762103217342747</v>
       </c>
       <c r="E19" s="12">
         <f t="shared" si="4"/>
-        <v>1.5919186678987549</v>
+        <v>1.5929271119943176</v>
       </c>
       <c r="F19" s="12">
         <f t="shared" si="4"/>
-        <v>1.1330912801880186</v>
+        <v>1.1338090676191737</v>
       </c>
       <c r="G19" s="12">
         <f t="shared" si="4"/>
-        <v>1.1248044571507001</v>
+        <v>1.1255169950688422</v>
       </c>
       <c r="H19" s="12">
         <f t="shared" si="4"/>
-        <v>1.3477206467041265</v>
+        <v>1.3485743969339861</v>
       </c>
       <c r="I19" s="12">
         <f t="shared" si="4"/>
-        <v>1.2871190452575807</v>
+        <v>1.2879344057578688</v>
       </c>
       <c r="J19" s="12">
         <f t="shared" si="4"/>
-        <v>1.271095816666254</v>
+        <v>1.2719010268174129</v>
       </c>
       <c r="K19" s="12">
         <f t="shared" si="4"/>
-        <v>1.1602087141469224</v>
+        <v>1.1609436798527686</v>
       </c>
       <c r="L19" s="12">
         <f t="shared" si="4"/>
-        <v>1.2827217171813321</v>
+        <v>1.2835342920747772</v>
       </c>
       <c r="M19" s="12">
         <f t="shared" si="4"/>
-        <v>1.0677432305455967</v>
+        <v>1.0684196214807202</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="4"/>
@@ -2060,47 +2060,47 @@
       </c>
       <c r="C20" s="12">
         <f t="shared" si="5"/>
-        <v>12.315002807419582</v>
+        <v>12.322804080259962</v>
       </c>
       <c r="D20" s="12">
         <f t="shared" si="5"/>
-        <v>7.3425045844242218</v>
+        <v>7.3471558932781944</v>
       </c>
       <c r="E20" s="12">
         <f t="shared" si="5"/>
-        <v>11.227998575659646</v>
+        <v>11.235111256160812</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="5"/>
-        <v>14.569281712118125</v>
+        <v>14.578511019126982</v>
       </c>
       <c r="G20" s="12">
         <f t="shared" si="5"/>
-        <v>26.64201742984082</v>
+        <v>26.658894539025333</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="5"/>
-        <v>6.9093078249553148</v>
+        <v>6.9136847135621284</v>
       </c>
       <c r="I20" s="12">
         <f t="shared" si="5"/>
-        <v>9.4806935771297969</v>
+        <v>9.4866993798460335</v>
       </c>
       <c r="J20" s="12">
         <f t="shared" si="5"/>
-        <v>12.568508395637913</v>
+        <v>12.576470258475</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="5"/>
-        <v>24.208138934551002</v>
+        <v>24.223474237330837</v>
       </c>
       <c r="L20" s="12">
         <f t="shared" si="5"/>
-        <v>18.248207735975285</v>
+        <v>18.259767558544759</v>
       </c>
       <c r="M20" s="12">
         <f t="shared" si="5"/>
-        <v>15.001801559878327</v>
+        <v>15.011304858326247</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="5"/>
@@ -2169,47 +2169,47 @@
       </c>
       <c r="C21" s="6">
         <f t="shared" si="6"/>
-        <v>156.31340326128225</v>
+        <v>156.2144449803985</v>
       </c>
       <c r="D21" s="6">
         <f t="shared" si="6"/>
-        <v>344.56907325150758</v>
+        <v>344.35093480385518</v>
       </c>
       <c r="E21" s="6">
         <f t="shared" si="6"/>
-        <v>207.51694830555431</v>
+        <v>207.38557428368469</v>
       </c>
       <c r="F21" s="6">
         <f t="shared" si="6"/>
-        <v>106.38822356703929</v>
+        <v>106.32087172458165</v>
       </c>
       <c r="G21" s="6">
         <f t="shared" si="6"/>
-        <v>58.55412429288095</v>
+        <v>58.517055075796648</v>
       </c>
       <c r="H21" s="6">
         <f t="shared" si="6"/>
-        <v>259.79447514507126</v>
+        <v>259.63000547000132</v>
       </c>
       <c r="I21" s="6">
         <f t="shared" si="6"/>
-        <v>180.36655083178931</v>
+        <v>180.25236507786892</v>
       </c>
       <c r="J21" s="6">
         <f t="shared" si="6"/>
-        <v>127.302297904762</v>
+        <v>127.22170586153106</v>
       </c>
       <c r="K21" s="6">
         <f t="shared" si="6"/>
-        <v>57.212163386226379</v>
+        <v>57.175943732529255</v>
       </c>
       <c r="L21" s="6">
         <f t="shared" si="6"/>
-        <v>80.007857271467515</v>
+        <v>79.957206208618189</v>
       </c>
       <c r="M21" s="6">
         <f t="shared" si="6"/>
-        <v>80.656979441462084</v>
+        <v>80.605917434876105</v>
       </c>
       <c r="N21" s="6">
         <f t="shared" si="6"/>
@@ -2558,7 +2558,18 @@
       <c r="J38" s="19"/>
       <c r="K38" s="19"/>
     </row>
-    <row r="39" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+    </row>
     <row r="40" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B40" s="19"/>
       <c r="C40" s="19"/>
@@ -2719,8 +2730,38 @@
       <c r="N49" s="19"/>
       <c r="O49" s="19"/>
     </row>
-    <row r="50" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="50" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="19"/>
+      <c r="J50" s="19"/>
+      <c r="K50" s="19"/>
+      <c r="L50" s="19"/>
+      <c r="M50" s="19"/>
+      <c r="N50" s="19"/>
+      <c r="O50" s="19"/>
+    </row>
+    <row r="51" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="19"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="19"/>
+      <c r="L51" s="19"/>
+      <c r="M51" s="19"/>
+      <c r="N51" s="19"/>
+      <c r="O51" s="19"/>
+    </row>
     <row r="52" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="53" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="54" spans="2:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
